--- a/attendance.xlsx
+++ b/attendance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,23 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>17:30:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>5024140_Sneha Nadar</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>15:51:04</t>
         </is>
       </c>
     </row>

--- a/attendance.xlsx
+++ b/attendance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,74 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>5024158_Aditi Shinde</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>11:34:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5024140_Sneha Nadar</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>11:34:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5024101_Rajiv Agarwal</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>11:35:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5024108_Renata Belli</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>11:35:58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/attendance.xlsx
+++ b/attendance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,6 +535,108 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5024170_Sonia Lotlikar</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>11:39:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5024114_Samruddhi Chondekar</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>11:39:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5024142_Navya Roshni</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>11:41:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5024122_Arya Gunjotikar</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>11:41:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>5024104_Samuel Alva</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>11:42:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5024128_Gabriel James</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>11:44:19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
